--- a/data/trans_orig/IP31KM02_R_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM02_R_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25833</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21569</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29505</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>69,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,62%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>28757</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23338</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33525</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>61,85%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>50,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>72,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31111</t>
+          <t>27121</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25981</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35420</t>
+          <t>31251</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>59868</t>
+          <t>52954</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53389</t>
+          <t>46790</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67185</t>
+          <t>58665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11602</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7930</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15866</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30,99%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,18%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,38%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>17738</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12970</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23157</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>38,15%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>15560</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19304</t>
+          <t>21027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>31911</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24594</t>
+          <t>21451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>33326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>116601</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>107414</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>123991</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>74,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,95%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>110805</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>100943</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>120121</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>69,56%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>63,37%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>75,41%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>132931</t>
+          <t>103134</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122538</t>
+          <t>94633</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>142083</t>
+          <t>110920</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>243736</t>
+          <t>219735</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>228282</t>
+          <t>207689</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>256921</t>
+          <t>232175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>76,74%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40441</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33051</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>49628</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>25,75%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,05%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>48494</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39178</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>58356</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30,44%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,63%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>49028</t>
+          <t>42384</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39876</t>
+          <t>34598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59421</t>
+          <t>50885</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>97523</t>
+          <t>82825</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84338</t>
+          <t>70385</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>112977</t>
+          <t>94871</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>133723</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>121802</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>145626</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>119581</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>108522</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>129794</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>69,09%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>62,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>74,99%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>139937</t>
+          <t>120325</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>126146</t>
+          <t>109476</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153794</t>
+          <t>130334</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>259518</t>
+          <t>254047</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243854</t>
+          <t>239120</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>275555</t>
+          <t>269789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>66403</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54500</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78324</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>53491</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>43278</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>64550</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>30,91%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25,01%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>37,3%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72553</t>
+          <t>54347</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58696</t>
+          <t>44338</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86344</t>
+          <t>65196</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>126045</t>
+          <t>120751</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110008</t>
+          <t>105009</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141709</t>
+          <t>135678</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>182846</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>164780</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>200984</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>62,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>56,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>68,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>144873</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>100371</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>166240</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>52,82%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>60,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>188508</t>
+          <t>150613</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>168274</t>
+          <t>137163</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>208738</t>
+          <t>167011</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>333382</t>
+          <t>333459</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>282335</t>
+          <t>309196</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>362706</t>
+          <t>356672</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>109375</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>91237</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>127441</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>37,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>31,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>43,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>129394</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>108027</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>173896</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>47,18%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>39,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>116491</t>
+          <t>104724</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96261</t>
+          <t>88326</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136725</t>
+          <t>118174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>245884</t>
+          <t>214099</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216560</t>
+          <t>190886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296931</t>
+          <t>238362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>43,53%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>459003</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>435647</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>481165</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66,83%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>63,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,06%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>594</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>404017</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>349862</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>434069</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>61,86%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>53,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,46%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>492487</t>
+          <t>401193</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>462686</t>
+          <t>380651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>516775</t>
+          <t>420442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>896504</t>
+          <t>860195</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>839638</t>
+          <t>828113</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>934115</t>
+          <t>890164</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>68,21%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>227821</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>205659</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>251177</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,17%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29,94%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>36,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>249117</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>219065</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>303272</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>38,14%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,54%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>46,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>252246</t>
+          <t>217015</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>227958</t>
+          <t>197766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>282047</t>
+          <t>237557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>501363</t>
+          <t>444836</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>463752</t>
+          <t>414867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>558229</t>
+          <t>476918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>36,54%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
